--- a/students/Navruzov Gamzabeg/Laba3/ЛР3_ОЦЕНКА_ПРОЕКТА (2).xlsx
+++ b/students/Navruzov Gamzabeg/Laba3/ЛР3_ОЦЕНКА_ПРОЕКТА (2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUAWEI\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\warrior\Desktop\it projecssdsadas\IT-project-management-AI-23\students\Navruzov Gamzabeg\Laba3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4C0B5B-1D53-4B2E-8DAB-A10D80E41FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405EBE2B-EF94-4D4D-8A0E-56292FED6EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -66,18 +63,6 @@
     <t>Работы</t>
   </si>
   <si>
-    <t>Оптимист
-(ч-д)</t>
-  </si>
-  <si>
-    <t>Реалист
-(ч-д)</t>
-  </si>
-  <si>
-    <t>Пессимист
-(ч-д)</t>
-  </si>
-  <si>
     <t>Ожидаемая оценка
 (ч-д)</t>
   </si>
@@ -362,6 +347,18 @@
   </si>
   <si>
     <t>Человеко месяцы</t>
+  </si>
+  <si>
+    <t>Оптимист
+часы</t>
+  </si>
+  <si>
+    <t>Реалист
+часы</t>
+  </si>
+  <si>
+    <t>Пессимист
+часы</t>
   </si>
 </sst>
 </file>
@@ -732,53 +729,53 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1046,47 +1043,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J91"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="84.69921875" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="84.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="16.19921875" customWidth="1"/>
-    <col min="8" max="9" width="15.69921875" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="G1" s="39" t="s">
-        <v>103</v>
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="52"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="38" t="s">
+        <v>100</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" s="42">
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="41">
         <f>E58</f>
         <v>1413</v>
       </c>
-      <c r="G2" s="42">
+      <c r="G2" s="41">
         <f>G58</f>
         <v>3165</v>
       </c>
@@ -1094,19 +1091,19 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="43" t="s">
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42">
+      <c r="E3" s="51"/>
+      <c r="F3" s="41">
         <f>F2/8</f>
         <v>176.625</v>
       </c>
-      <c r="G3" s="42">
+      <c r="G3" s="41">
         <f>G2/8</f>
         <v>395.625</v>
       </c>
@@ -1114,19 +1111,19 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42">
+    <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="51"/>
+      <c r="F4" s="41">
         <f>F3/22</f>
         <v>8.0284090909090917</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="41">
         <f>G3/22</f>
         <v>17.982954545454547</v>
       </c>
@@ -1134,19 +1131,19 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="43" t="s">
+    <row r="5" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="52"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="42">
+      <c r="E5" s="51"/>
+      <c r="F5" s="41">
         <f>F4/2</f>
         <v>4.0142045454545459</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="41">
         <f>G4/2</f>
         <v>8.9914772727272734</v>
       </c>
@@ -1154,40 +1151,38 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="43" t="s">
+    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="52"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="43"/>
-      <c r="F6" s="44">
+      <c r="E6" s="51"/>
+      <c r="F6" s="42">
         <v>300</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="42">
         <v>350</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="45" t="s">
+    <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="46">
-        <f>F6*H58</f>
-        <v>2008500</v>
-      </c>
-      <c r="G7" s="46">
-        <f>G6*H90</f>
-        <v>0</v>
+      <c r="E7" s="50"/>
+      <c r="F7" s="43">
+        <v>257000</v>
+      </c>
+      <c r="G7" s="43">
+        <v>378000</v>
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -1197,48 +1192,48 @@
       <c r="C8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="47" t="s">
+      <c r="E8" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="H8" s="44" t="s">
         <v>8</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="47" t="s">
-        <v>11</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="50"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="52"/>
+        <v>10</v>
+      </c>
+      <c r="E9" s="47"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="49"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="9">
         <v>1.1000000000000001</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -1247,14 +1242,14 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E11" s="15">
         <v>26</v>
@@ -1272,14 +1267,14 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19"/>
       <c r="B12" s="19"/>
       <c r="C12" s="13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12" s="15">
         <v>39</v>
@@ -1296,14 +1291,14 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19"/>
       <c r="B13" s="19"/>
       <c r="C13" s="13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E13" s="15">
         <v>52</v>
@@ -1320,14 +1315,14 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19"/>
       <c r="B14" s="19"/>
       <c r="C14" s="13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E14" s="15">
         <v>26</v>
@@ -1344,14 +1339,14 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19"/>
       <c r="B15" s="19"/>
       <c r="C15" s="13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E15" s="15">
         <v>13</v>
@@ -1368,16 +1363,16 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="9">
         <v>1.2</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
@@ -1385,14 +1380,14 @@
       <c r="H16" s="18"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19"/>
       <c r="B17" s="19"/>
       <c r="C17" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E17" s="15">
         <v>26</v>
@@ -1409,14 +1404,14 @@
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
       <c r="B18" s="19"/>
       <c r="C18" s="13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E18" s="15">
         <v>26</v>
@@ -1433,14 +1428,14 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19"/>
       <c r="B19" s="19"/>
       <c r="C19" s="13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" s="15">
         <v>26</v>
@@ -1457,14 +1452,14 @@
       </c>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
@@ -1472,14 +1467,14 @@
       <c r="H20" s="18"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E21" s="15">
         <v>26</v>
@@ -1496,14 +1491,14 @@
       </c>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19"/>
       <c r="B22" s="19"/>
       <c r="C22" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E22" s="15">
         <v>19</v>
@@ -1520,14 +1515,14 @@
       </c>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19"/>
       <c r="B23" s="19"/>
       <c r="C23" s="13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E23" s="15">
         <v>13</v>
@@ -1544,14 +1539,14 @@
       </c>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9">
         <v>1.4</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
@@ -1559,14 +1554,14 @@
       <c r="H24" s="18"/>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19"/>
       <c r="B25" s="19"/>
       <c r="C25" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E25" s="15">
         <v>26</v>
@@ -1583,14 +1578,14 @@
       </c>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19"/>
       <c r="B26" s="19"/>
       <c r="C26" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E26" s="15">
         <v>19</v>
@@ -1607,14 +1602,14 @@
       </c>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19"/>
       <c r="B27" s="19"/>
       <c r="C27" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E27" s="15">
         <v>26</v>
@@ -1631,14 +1626,14 @@
       </c>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9">
         <v>1.5</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
@@ -1646,14 +1641,14 @@
       <c r="H28" s="18"/>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19"/>
       <c r="B29" s="19"/>
       <c r="C29" s="13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E29" s="23">
         <v>39</v>
@@ -1670,14 +1665,14 @@
       </c>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19"/>
       <c r="B30" s="19"/>
       <c r="C30" s="13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E30" s="23">
         <v>65</v>
@@ -1694,14 +1689,14 @@
       </c>
       <c r="J30" s="1"/>
     </row>
-    <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="26"/>
       <c r="B31" s="26"/>
       <c r="C31" s="9">
         <v>1.6</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
@@ -1709,14 +1704,14 @@
       <c r="H31" s="18"/>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E32" s="29">
         <v>52</v>
@@ -1733,14 +1728,14 @@
       </c>
       <c r="J32" s="1"/>
     </row>
-    <row r="33" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19"/>
       <c r="B33" s="19"/>
       <c r="C33" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E33" s="23">
         <v>26</v>
@@ -1757,14 +1752,14 @@
       </c>
       <c r="J33" s="1"/>
     </row>
-    <row r="34" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20"/>
       <c r="B34" s="20"/>
       <c r="C34" s="9">
         <v>1.7</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
@@ -1772,14 +1767,14 @@
       <c r="H34" s="18"/>
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19"/>
       <c r="B35" s="19"/>
       <c r="C35" s="13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E35" s="23">
         <v>26</v>
@@ -1794,19 +1789,16 @@
         <f>SUM(E35:G35)</f>
         <v>111</v>
       </c>
-      <c r="J35" s="49">
-        <f>SUM(H11:H36)</f>
-        <v>2862</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J35" s="46"/>
+    </row>
+    <row r="36" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19"/>
       <c r="B36" s="19"/>
       <c r="C36" s="13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E36" s="23">
         <v>39</v>
@@ -1822,27 +1814,27 @@
         <v>156</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="19"/>
       <c r="C37" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="24"/>
       <c r="G37" s="25"/>
       <c r="H37" s="18"/>
     </row>
-    <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19"/>
       <c r="B38" s="19"/>
       <c r="C38" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E38" s="23">
         <v>78</v>
@@ -1858,13 +1850,13 @@
         <v>334</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="19"/>
       <c r="C39" s="13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E39" s="23">
         <v>65</v>
@@ -1880,14 +1872,14 @@
         <v>289</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19"/>
       <c r="B40" s="19"/>
       <c r="C40" s="13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E40" s="23">
         <v>39</v>
@@ -1903,13 +1895,13 @@
         <v>178</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="19"/>
       <c r="C41" s="13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E41" s="23">
         <v>39</v>
@@ -1925,14 +1917,14 @@
         <v>199</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19"/>
       <c r="B42" s="19"/>
       <c r="C42" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E42" s="23">
         <v>52</v>
@@ -1948,27 +1940,27 @@
         <v>233</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="19"/>
       <c r="C43" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E43" s="23"/>
       <c r="F43" s="24"/>
       <c r="G43" s="25"/>
       <c r="H43" s="18"/>
     </row>
-    <row r="44" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19"/>
       <c r="B44" s="19"/>
       <c r="C44" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E44" s="23">
         <v>39</v>
@@ -1984,13 +1976,13 @@
         <v>188</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="19"/>
       <c r="C45" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E45" s="23">
         <v>26</v>
@@ -2006,14 +1998,14 @@
         <v>127</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19"/>
       <c r="B46" s="19"/>
       <c r="C46" s="13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E46" s="23">
         <v>78</v>
@@ -2029,13 +2021,13 @@
         <v>334</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="19"/>
       <c r="C47" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E47" s="23">
         <v>26</v>
@@ -2051,27 +2043,27 @@
         <v>127</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19"/>
       <c r="B48" s="19"/>
       <c r="C48" s="13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E48" s="23"/>
       <c r="F48" s="24"/>
       <c r="G48" s="25"/>
       <c r="H48" s="18"/>
     </row>
-    <row r="49" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="19"/>
       <c r="C49" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E49" s="23">
         <v>45</v>
@@ -2087,14 +2079,14 @@
         <v>205</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19"/>
       <c r="B50" s="19"/>
       <c r="C50" s="13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E50" s="23">
         <v>32</v>
@@ -2110,13 +2102,13 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="19"/>
       <c r="C51" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E51" s="23">
         <v>32</v>
@@ -2132,27 +2124,27 @@
         <v>139</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19"/>
       <c r="B52" s="19"/>
       <c r="C52" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E52" s="23"/>
       <c r="F52" s="24"/>
       <c r="G52" s="25"/>
       <c r="H52" s="18"/>
     </row>
-    <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="19"/>
       <c r="C53" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E53" s="23">
         <v>26</v>
@@ -2168,14 +2160,14 @@
         <v>143</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19"/>
       <c r="B54" s="19"/>
       <c r="C54" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E54" s="23">
         <v>129</v>
@@ -2191,13 +2183,13 @@
         <v>661</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="19"/>
       <c r="C55" s="13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E55" s="23">
         <v>97</v>
@@ -2213,7 +2205,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
       <c r="C56" s="31"/>
@@ -2222,7 +2214,7 @@
       <c r="F56" s="24"/>
       <c r="G56" s="25"/>
     </row>
-    <row r="57" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="C57" s="32"/>
@@ -2231,9 +2223,9 @@
       <c r="F57" s="34"/>
       <c r="G57" s="35"/>
     </row>
-    <row r="58" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="36" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="32"/>
@@ -2255,95 +2247,95 @@
         <v>6695</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="1"/>
     </row>
-    <row r="60" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="1"/>
     </row>
-    <row r="61" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="1"/>
     </row>
-    <row r="62" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="1"/>
     </row>
-    <row r="63" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1"/>
     </row>
-    <row r="64" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="1"/>
     </row>
-    <row r="66" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="1"/>
     </row>
-    <row r="67" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="1"/>
     </row>
-    <row r="68" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="1"/>
     </row>
-    <row r="70" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="1"/>
     </row>
-    <row r="71" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="1"/>
     </row>
-    <row r="72" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="1"/>
     </row>
-    <row r="73" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="1"/>
     </row>
-    <row r="74" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="1"/>
     </row>
-    <row r="75" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="1"/>
     </row>
-    <row r="76" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="1"/>
     </row>
-    <row r="77" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="1"/>
     </row>
-    <row r="78" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="1"/>
     </row>
-    <row r="79" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="1"/>
     </row>
-    <row r="80" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="1"/>
     </row>
-    <row r="81" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="1"/>
     </row>
-    <row r="82" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="1"/>
     </row>
-    <row r="84" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="1"/>
     </row>
-    <row r="85" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J86" s="1"/>
     </row>
-    <row r="87" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J87" s="1"/>
     </row>
-    <row r="88" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J88" s="1"/>
     </row>
-    <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2353,7 +2345,7 @@
       <c r="G89" s="1"/>
       <c r="J89" s="1"/>
     </row>
-    <row r="90" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -2363,7 +2355,7 @@
       <c r="G90" s="1"/>
       <c r="J90" s="1"/>
     </row>
-    <row r="91" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -2375,12 +2367,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:C6"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A1:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/students/Navruzov Gamzabeg/Laba3/ЛР3_ОЦЕНКА_ПРОЕКТА (2).xlsx
+++ b/students/Navruzov Gamzabeg/Laba3/ЛР3_ОЦЕНКА_ПРОЕКТА (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\warrior\Desktop\it projecssdsadas\IT-project-management-AI-23\students\Navruzov Gamzabeg\Laba3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405EBE2B-EF94-4D4D-8A0E-56292FED6EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF0BE00-E9D0-48B9-A4A5-F9DC767850D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -211,9 +211,6 @@
     <t>1.7.1</t>
   </si>
   <si>
-    <t>Адаптивность + поддержка Chrome/Firefox</t>
-  </si>
-  <si>
     <t>1.7.2</t>
   </si>
   <si>
@@ -359,6 +356,9 @@
   <si>
     <t>Пессимист
 часы</t>
+  </si>
+  <si>
+    <t>Адаптивность</t>
   </si>
 </sst>
 </file>
@@ -768,14 +768,14 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1056,28 +1056,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52"/>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
+      <c r="A1" s="50"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
       <c r="D1" s="37"/>
       <c r="E1" s="37"/>
       <c r="F1" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="38" t="s">
         <v>99</v>
-      </c>
-      <c r="G1" s="38" t="s">
-        <v>100</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
       <c r="D2" s="39"/>
       <c r="E2" s="40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F2" s="41">
         <f>E58</f>
@@ -1092,13 +1092,13 @@
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="51" t="s">
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="51"/>
+      <c r="E3" s="52"/>
       <c r="F3" s="41">
         <f>F2/8</f>
         <v>176.625</v>
@@ -1112,13 +1112,13 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="51"/>
+      <c r="A4" s="50"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="52"/>
       <c r="F4" s="41">
         <f>F3/22</f>
         <v>8.0284090909090917</v>
@@ -1132,13 +1132,13 @@
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="51" t="s">
+      <c r="A5" s="50"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="51"/>
+      <c r="E5" s="52"/>
       <c r="F5" s="41">
         <f>F4/2</f>
         <v>4.0142045454545459</v>
@@ -1152,13 +1152,13 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="51" t="s">
+      <c r="A6" s="50"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="51"/>
+      <c r="E6" s="52"/>
       <c r="F6" s="42">
         <v>300</v>
       </c>
@@ -1170,10 +1170,10 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="50" t="s">
+      <c r="D7" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="50"/>
+      <c r="E7" s="51"/>
       <c r="F7" s="43">
         <v>257000</v>
       </c>
@@ -1196,13 +1196,13 @@
         <v>7</v>
       </c>
       <c r="E8" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="G8" s="45" t="s">
         <v>104</v>
-      </c>
-      <c r="G8" s="45" t="s">
-        <v>105</v>
       </c>
       <c r="H8" s="44" t="s">
         <v>8</v>
@@ -1774,7 +1774,7 @@
         <v>56</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="E35" s="23">
         <v>26</v>
@@ -1795,10 +1795,10 @@
       <c r="A36" s="19"/>
       <c r="B36" s="19"/>
       <c r="C36" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="E36" s="23">
         <v>39</v>
@@ -1817,10 +1817,10 @@
     <row r="37" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="19"/>
       <c r="C37" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>60</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>61</v>
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="24"/>
@@ -1831,10 +1831,10 @@
       <c r="A38" s="19"/>
       <c r="B38" s="19"/>
       <c r="C38" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" s="21" t="s">
         <v>62</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>63</v>
       </c>
       <c r="E38" s="23">
         <v>78</v>
@@ -1853,10 +1853,10 @@
     <row r="39" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="19"/>
       <c r="C39" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" s="21" t="s">
         <v>64</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>65</v>
       </c>
       <c r="E39" s="23">
         <v>65</v>
@@ -1876,10 +1876,10 @@
       <c r="A40" s="19"/>
       <c r="B40" s="19"/>
       <c r="C40" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="21" t="s">
         <v>66</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>67</v>
       </c>
       <c r="E40" s="23">
         <v>39</v>
@@ -1898,10 +1898,10 @@
     <row r="41" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="19"/>
       <c r="C41" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="E41" s="23">
         <v>39</v>
@@ -1921,10 +1921,10 @@
       <c r="A42" s="19"/>
       <c r="B42" s="19"/>
       <c r="C42" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" s="21" t="s">
         <v>70</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>71</v>
       </c>
       <c r="E42" s="23">
         <v>52</v>
@@ -1943,10 +1943,10 @@
     <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="19"/>
       <c r="C43" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D43" s="10" t="s">
         <v>72</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="E43" s="23"/>
       <c r="F43" s="24"/>
@@ -1957,10 +1957,10 @@
       <c r="A44" s="19"/>
       <c r="B44" s="19"/>
       <c r="C44" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" s="21" t="s">
         <v>74</v>
-      </c>
-      <c r="D44" s="21" t="s">
-        <v>75</v>
       </c>
       <c r="E44" s="23">
         <v>39</v>
@@ -1979,10 +1979,10 @@
     <row r="45" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="19"/>
       <c r="C45" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="E45" s="23">
         <v>26</v>
@@ -2002,10 +2002,10 @@
       <c r="A46" s="19"/>
       <c r="B46" s="19"/>
       <c r="C46" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D46" s="21" t="s">
         <v>78</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>79</v>
       </c>
       <c r="E46" s="23">
         <v>78</v>
@@ -2024,10 +2024,10 @@
     <row r="47" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="19"/>
       <c r="C47" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="E47" s="23">
         <v>26</v>
@@ -2047,10 +2047,10 @@
       <c r="A48" s="19"/>
       <c r="B48" s="19"/>
       <c r="C48" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="E48" s="23"/>
       <c r="F48" s="24"/>
@@ -2060,10 +2060,10 @@
     <row r="49" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="19"/>
       <c r="C49" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D49" s="21" t="s">
         <v>84</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>85</v>
       </c>
       <c r="E49" s="23">
         <v>45</v>
@@ -2083,10 +2083,10 @@
       <c r="A50" s="19"/>
       <c r="B50" s="19"/>
       <c r="C50" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D50" s="21" t="s">
         <v>86</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>87</v>
       </c>
       <c r="E50" s="23">
         <v>32</v>
@@ -2105,10 +2105,10 @@
     <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="19"/>
       <c r="C51" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="E51" s="23">
         <v>32</v>
@@ -2128,10 +2128,10 @@
       <c r="A52" s="19"/>
       <c r="B52" s="19"/>
       <c r="C52" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D52" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="E52" s="23"/>
       <c r="F52" s="24"/>
@@ -2141,10 +2141,10 @@
     <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="19"/>
       <c r="C53" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="21" t="s">
         <v>92</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>93</v>
       </c>
       <c r="E53" s="23">
         <v>26</v>
@@ -2164,10 +2164,10 @@
       <c r="A54" s="19"/>
       <c r="B54" s="19"/>
       <c r="C54" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D54" s="21" t="s">
         <v>94</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>95</v>
       </c>
       <c r="E54" s="23">
         <v>129</v>
@@ -2186,10 +2186,10 @@
     <row r="55" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="19"/>
       <c r="C55" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>96</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>97</v>
       </c>
       <c r="E55" s="23">
         <v>97</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="58" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="32"/>
